--- a/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 27,18</t>
+          <t>1,62; 25,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 41,47</t>
+          <t>12,66; 40,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 27,03</t>
+          <t>-11,39; 27,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 10,85</t>
+          <t>-17,98; 11,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 17,41</t>
+          <t>-12,2; 17,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -0,05</t>
+          <t>-30,39; 0,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 14,56</t>
+          <t>-5,05; 14,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 25,07</t>
+          <t>4,68; 24,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 9,25</t>
+          <t>-15,41; 9,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 109,64</t>
+          <t>4,27; 100,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 167,87</t>
+          <t>32,1; 155,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 96,25</t>
+          <t>-33,78; 101,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 25,25</t>
+          <t>-31,98; 27,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 40,94</t>
+          <t>-21,56; 39,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -0,02</t>
+          <t>-54,52; 0,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 41,7</t>
+          <t>-12,4; 41,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 69,38</t>
+          <t>10,46; 69,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 24,7</t>
+          <t>-35,06; 25,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,82</t>
+          <t>0,41; 12,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,18</t>
+          <t>-7,24; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -0,89</t>
+          <t>-14,84; -1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,88</t>
+          <t>-2,48; 9,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 1,05</t>
+          <t>-10,79; 1,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 0,61</t>
+          <t>-12,72; 0,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,16</t>
+          <t>0,86; 8,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,77</t>
+          <t>-7,23; 0,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -1,35</t>
+          <t>-11,66; -1,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 39,26</t>
+          <t>0,98; 38,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 12,56</t>
+          <t>-19,56; 12,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,5; -3,69</t>
+          <t>-38,67; -4,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 19,27</t>
+          <t>-4,83; 20,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 2,28</t>
+          <t>-21,17; 3,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 1,33</t>
+          <t>-25,73; -0,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 22,38</t>
+          <t>1,89; 21,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 1,82</t>
+          <t>-16,21; 1,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; -3,38</t>
+          <t>-26,61; -3,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 12,42</t>
+          <t>-6,1; 13,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 1,33</t>
+          <t>-16,77; 1,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,63; -4,95</t>
+          <t>-21,91; -3,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 25,8</t>
+          <t>5,9; 25,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 20,81</t>
+          <t>0,24; 20,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 6,24</t>
+          <t>-11,75; 6,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,62</t>
+          <t>2,89; 16,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 8,32</t>
+          <t>-4,91; 8,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -0,58</t>
+          <t>-14,43; -1,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 38,11</t>
+          <t>-15,27; 44,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 4,57</t>
+          <t>-41,51; 4,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,59; -13,17</t>
+          <t>-54,96; -11,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,09; 95,08</t>
+          <t>14,83; 91,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 73,53</t>
+          <t>-0,02; 73,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,26; 21,39</t>
+          <t>-31,11; 24,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,48; 53,36</t>
+          <t>7,7; 53,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 26,62</t>
+          <t>-12,59; 26,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -1,87</t>
+          <t>-38,06; -6,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,51</t>
+          <t>2,04; 11,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,31</t>
+          <t>-5,07; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -2,31</t>
+          <t>-12,67; -1,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,2</t>
+          <t>0,21; 9,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,46</t>
+          <t>-5,29; 4,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,14</t>
+          <t>-11,59; -1,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,27</t>
+          <t>2,25; 9,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,5</t>
+          <t>-3,72; 3,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; -2,9</t>
+          <t>-10,27; -2,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 35,38</t>
+          <t>5,64; 35,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 13,13</t>
+          <t>-13,37; 12,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,8; -6,62</t>
+          <t>-33,93; -5,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 23,48</t>
+          <t>0,41; 22,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 10,07</t>
+          <t>-11,35; 9,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -2,62</t>
+          <t>-24,39; -2,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13; 24,01</t>
+          <t>5,29; 23,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 6,44</t>
+          <t>-8,93; 7,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -7,4</t>
+          <t>-24,65; -7,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 25,69</t>
+          <t>-0,42; 25,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 40,55</t>
+          <t>11,57; 41,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 27,12</t>
+          <t>-12,45; 25,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 11,33</t>
+          <t>-15,82; 12,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 17,51</t>
+          <t>-12,9; 16,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 0,04</t>
+          <t>-31,05; -1,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 14,62</t>
+          <t>-3,96; 14,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 24,84</t>
+          <t>5,63; 25,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 9,15</t>
+          <t>-15,17; 9,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 100,55</t>
+          <t>-1,16; 98,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,1; 155,67</t>
+          <t>29,34; 161,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 101,72</t>
+          <t>-34,05; 94,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 27,78</t>
+          <t>-27,95; 30,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 39,12</t>
+          <t>-22,51; 38,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 0,19</t>
+          <t>-55,03; -2,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 41,0</t>
+          <t>-8,75; 41,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 69,99</t>
+          <t>12,81; 75,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 25,61</t>
+          <t>-35,98; 27,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 12,57</t>
+          <t>1,06; 13,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,06</t>
+          <t>-7,58; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -1,5</t>
+          <t>-13,72; -1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 9,37</t>
+          <t>-2,1; 8,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 1,46</t>
+          <t>-10,27; 1,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 0,06</t>
+          <t>-12,23; 0,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,84</t>
+          <t>0,69; 9,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,64</t>
+          <t>-7,29; 0,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; -1,68</t>
+          <t>-11,32; -1,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 38,14</t>
+          <t>2,5; 39,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 12,39</t>
+          <t>-19,2; 12,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,67; -4,32</t>
+          <t>-35,91; -4,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 20,33</t>
+          <t>-4,23; 19,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 3,15</t>
+          <t>-19,97; 2,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; -0,11</t>
+          <t>-24,11; 0,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 21,72</t>
+          <t>1,62; 22,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 1,4</t>
+          <t>-16,25; 2,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,61; -3,81</t>
+          <t>-26,28; -3,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 13,66</t>
+          <t>-6,11; 13,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 1,49</t>
+          <t>-16,81; 1,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,91; -3,71</t>
+          <t>-21,65; -4,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 25,67</t>
+          <t>5,8; 25,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 20,24</t>
+          <t>0,59; 19,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 6,49</t>
+          <t>-12,48; 6,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 16,43</t>
+          <t>2,76; 16,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 8,4</t>
+          <t>-5,16; 9,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -1,94</t>
+          <t>-13,72; -0,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 44,65</t>
+          <t>-15,71; 40,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 4,83</t>
+          <t>-41,22; 5,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,96; -11,57</t>
+          <t>-54,43; -14,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,83; 91,61</t>
+          <t>14,86; 89,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 73,46</t>
+          <t>1,46; 70,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 24,42</t>
+          <t>-32,47; 23,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,7; 53,09</t>
+          <t>6,79; 51,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 26,05</t>
+          <t>-13,32; 29,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,06; -6,13</t>
+          <t>-35,78; -2,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,6</t>
+          <t>1,83; 11,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,02</t>
+          <t>-5,25; 4,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; -1,9</t>
+          <t>-12,57; -2,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 9,85</t>
+          <t>0,75; 10,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 4,11</t>
+          <t>-5,36; 3,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -1,2</t>
+          <t>-11,85; -1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,14</t>
+          <t>2,6; 9,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,11</t>
+          <t>-3,83; 2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -2,79</t>
+          <t>-10,22; -2,81</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,64; 35,67</t>
+          <t>4,78; 34,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 12,2</t>
+          <t>-14,07; 12,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,93; -5,73</t>
+          <t>-33,82; -8,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 22,84</t>
+          <t>1,42; 22,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 9,58</t>
+          <t>-11,06; 8,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,39; -2,83</t>
+          <t>-24,43; -3,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 23,36</t>
+          <t>6,14; 24,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 7,99</t>
+          <t>-9,11; 6,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,65; -7,18</t>
+          <t>-24,93; -7,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_R2-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-14,19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13,35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>27,24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-15,41</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-4,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 25,37</t>
+          <t>-17,17; 10,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 41,1</t>
+          <t>-12,42; 17,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 25,57</t>
+          <t>-29,23; 1,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 12,84</t>
+          <t>1,1; 27,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 16,34</t>
+          <t>14,31; 41,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -1,3</t>
+          <t>-11,71; 19,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 14,8</t>
+          <t>-4,32; 14,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 25,98</t>
+          <t>5,02; 25,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 9,54</t>
+          <t>-15,12; 7,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,39%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-28,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>43,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>87,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,39%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,79%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>-10,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 98,14</t>
+          <t>-30,44; 25,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,34; 161,07</t>
+          <t>-22,7; 40,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 94,91</t>
+          <t>-52,75; 3,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 30,76</t>
+          <t>2,35; 109,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,51; 38,27</t>
+          <t>37,15; 167,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,03; -2,13</t>
+          <t>-33,34; 76,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 41,53</t>
+          <t>-9,83; 41,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,81; 75,02</t>
+          <t>11,69; 69,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 27,87</t>
+          <t>-34,43; 21,87</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-4,42</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,74</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,61</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-7,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,11</t>
+          <t>-5,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,58</t>
+          <t>-5,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 13,08</t>
+          <t>-3,06; 8,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 4,07</t>
+          <t>-10,49; 1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -1,45</t>
+          <t>-12,22; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 8,91</t>
+          <t>0,68; 12,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 1,01</t>
+          <t>-7,48; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 0,21</t>
+          <t>-11,08; 0,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 9,22</t>
+          <t>0,96; 9,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,96</t>
+          <t>-7,36; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-11,32; -1,24</t>
+          <t>-9,94; -1,03</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-9,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-11,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>19,48%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-4,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-19,75%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,14%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,64%</t>
+          <t>-16,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,49%</t>
+          <t>-13,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 39,53</t>
+          <t>-6,07; 19,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 12,56</t>
+          <t>-20,47; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -4,47</t>
+          <t>-23,97; 2,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 19,51</t>
+          <t>1,88; 39,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 2,38</t>
+          <t>-19,58; 12,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 0,5</t>
+          <t>-29,07; 0,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 22,85</t>
+          <t>2,0; 22,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 2,45</t>
+          <t>-16,63; 1,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,28; -3,26</t>
+          <t>-22,43; -2,32</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-7,94</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-13,21</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,52</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-14,07</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-8,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 13,33</t>
+          <t>6,2; 25,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 1,91</t>
+          <t>-0,09; 20,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,65; -4,75</t>
+          <t>-12,32; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 25,12</t>
+          <t>-6,89; 12,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 19,99</t>
+          <t>-17,01; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 6,76</t>
+          <t>-23,23; -5,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 16,62</t>
+          <t>2,7; 16,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 9,12</t>
+          <t>-5,13; 8,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -0,7</t>
+          <t>-15,01; -1,06</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-7,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,53%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-21,8%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,29%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-38,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-22,57%</t>
+          <t>-23,91%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 40,47</t>
+          <t>16,09; 95,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 5,65</t>
+          <t>-0,02; 73,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -14,49</t>
+          <t>-33,35; 22,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,86; 89,79</t>
+          <t>-17,89; 38,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 70,45</t>
+          <t>-41,21; 4,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 23,89</t>
+          <t>-56,39; -16,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 51,79</t>
+          <t>6,48; 53,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 29,31</t>
+          <t>-13,93; 26,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,78; -2,25</t>
+          <t>-39,15; -3,51</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,05</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,09</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,42</t>
+          <t>-6,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,52</t>
+          <t>-6,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,66</t>
+          <t>0,39; 10,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,14</t>
+          <t>-5,13; 4,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -2,7</t>
+          <t>-11,69; -1,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 10,02</t>
+          <t>2,48; 11,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,84</t>
+          <t>-4,92; 4,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,85; -1,55</t>
+          <t>-10,91; -1,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,28</t>
+          <t>2,52; 9,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,57</t>
+          <t>-3,78; 2,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -2,81</t>
+          <t>-9,52; -2,73</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,52%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-13,31%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-1,04%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-14,14%</t>
+          <t>-19,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,13%</t>
+          <t>-15,39%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 34,78</t>
+          <t>0,37; 23,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 12,54</t>
+          <t>-10,85; 10,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -8,09</t>
+          <t>-24,75; -2,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 22,6</t>
+          <t>6,62; 35,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 8,93</t>
+          <t>-13,21; 13,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -3,51</t>
+          <t>-29,38; -5,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,14; 24,22</t>
+          <t>6,13; 24,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 6,6</t>
+          <t>-9,02; 6,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -7,31</t>
+          <t>-22,99; -7,07</t>
         </is>
       </c>
     </row>
